--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_los lagos.xlsx
@@ -111,15 +111,15 @@
     <t xml:space="preserve">Los Muermos</t>
   </si>
   <si>
+    <t xml:space="preserve">Río Negro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fresia</t>
   </si>
   <si>
     <t xml:space="preserve">Purranque</t>
   </si>
   <si>
-    <t xml:space="preserve">Río Negro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Puyehue</t>
   </si>
   <si>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:22</t>
+    <t xml:space="preserve">2026-09-09 23:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -990,7 +990,7 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>10104</v>
+        <v>10305</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2022</v>
@@ -1007,7 +1007,7 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>10303</v>
+        <v>10104</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2022</v>
@@ -1024,7 +1024,7 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>10305</v>
+        <v>10303</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2022</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:18</t>
+    <t xml:space="preserve">2026-09-17 14:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_los lagos.xlsx
@@ -111,15 +111,15 @@
     <t xml:space="preserve">Los Muermos</t>
   </si>
   <si>
+    <t xml:space="preserve">Fresia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purranque</t>
+  </si>
+  <si>
     <t xml:space="preserve">Río Negro</t>
   </si>
   <si>
-    <t xml:space="preserve">Fresia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purranque</t>
-  </si>
-  <si>
     <t xml:space="preserve">Puyehue</t>
   </si>
   <si>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:14</t>
+    <t xml:space="preserve">2026-09-23 12:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -990,7 +990,7 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>10305</v>
+        <v>10104</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2022</v>
@@ -1007,7 +1007,7 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>10104</v>
+        <v>10303</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2022</v>
@@ -1024,7 +1024,7 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>10303</v>
+        <v>10305</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2022</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:42</t>
+    <t xml:space="preserve">2026-10-02 14:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:59</t>
+    <t xml:space="preserve">2026-10-05 11:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
